--- a/src/test/resources/testData/testData.xlsx
+++ b/src/test/resources/testData/testData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Login" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,34 +11,118 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>scenarioname</t>
-  </si>
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>Login valid credentials</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>validCredentials</t>
+  </si>
+  <si>
+    <t>qasquad</t>
+  </si>
+  <si>
+    <t>learners@123</t>
+  </si>
+  <si>
+    <t>nonExisting</t>
+  </si>
+  <si>
+    <t>notexisted</t>
+  </si>
+  <si>
+    <t>not@123</t>
+  </si>
+  <si>
+    <t>bothFieldsempty</t>
+  </si>
+  <si>
+    <t>username empty</t>
+  </si>
+  <si>
+    <t>Diet@123</t>
+  </si>
+  <si>
+    <t>password empty</t>
+  </si>
+  <si>
+    <t>Diet123</t>
+  </si>
+  <si>
+    <t>specialCharacters in username</t>
+  </si>
+  <si>
+    <t>##%&amp;*</t>
+  </si>
+  <si>
+    <t>specialCharacters in password</t>
+  </si>
+  <si>
+    <t>%$#&amp;*</t>
+  </si>
+  <si>
+    <t>shortUsername</t>
+  </si>
+  <si>
+    <t>Diet</t>
+  </si>
+  <si>
+    <t>shortpassword</t>
+  </si>
+  <si>
+    <t>Dietitian</t>
+  </si>
+  <si>
+    <t>die</t>
+  </si>
+  <si>
+    <t>wrongPassword</t>
+  </si>
+  <si>
+    <t>wrongUsername</t>
+  </si>
+  <si>
+    <t>Dietitan123</t>
+  </si>
+  <si>
+    <t>longlengthInUsername</t>
+  </si>
+  <si>
+    <t>Dietitan123jfjfkf</t>
+  </si>
+  <si>
+    <t>Dietitan124</t>
+  </si>
+  <si>
+    <t>longlengthInPassword</t>
   </si>
   <si>
     <t>Dietitan</t>
   </si>
   <si>
-    <t>Dietitian123</t>
-  </si>
-  <si>
-    <t>Login invalid credentials</t>
+    <t>Dietitan123tttttttt</t>
+  </si>
+  <si>
+    <t>specialCharactersInboth</t>
+  </si>
+  <si>
+    <t>$$$</t>
+  </si>
+  <si>
+    <t>@$$</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -46,31 +130,79 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -289,8 +421,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="23.25"/>
-    <col customWidth="1" min="2" max="2" width="18.88"/>
+    <col customWidth="1" min="1" max="1" width="24.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -303,10 +434,9 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -317,9 +447,155 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
